--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Desktop\intern\Sarochinee\งาน\PJ Intern\Code-PJ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Desktop\Code-PJ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37E13044-0464-4E59-80F9-5B500F876418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FFB238-26F5-49A0-A8D5-512350B55973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6540" yWindow="1185" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,9 +31,6 @@
     <t>Model</t>
   </si>
   <si>
-    <t>192.168.0.55</t>
-  </si>
-  <si>
     <t>Username</t>
   </si>
   <si>
@@ -74,6 +71,9 @@
   </si>
   <si>
     <t>H3C</t>
+  </si>
+  <si>
+    <t>192.168.100.120</t>
   </si>
 </sst>
 </file>
@@ -466,10 +466,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -477,64 +477,64 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
         <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -1,111 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Desktop\Code-PJ\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FFB238-26F5-49A0-A8D5-512350B55973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
-  <si>
-    <t>IP</t>
-  </si>
-  <si>
-    <t>Brand</t>
-  </si>
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>admin-Ppond</t>
-  </si>
-  <si>
-    <t>WS-C2960-24LC-S</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>Cisco</t>
-  </si>
-  <si>
-    <t>0.0.0.0</t>
-  </si>
-  <si>
-    <t>HPE</t>
-  </si>
-  <si>
-    <t>0.0.0.1</t>
-  </si>
-  <si>
-    <t>0.0.0.2</t>
-  </si>
-  <si>
-    <t>0.0.0.3</t>
-  </si>
-  <si>
-    <t>0.0.0.4</t>
-  </si>
-  <si>
-    <t>H3C</t>
-  </si>
-  <si>
-    <t>192.168.100.120</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -120,50 +46,100 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -201,7 +177,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -235,7 +211,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -270,10 +245,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -446,100 +420,137 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E9" t="s">
-        <v>8</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Username</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Password</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>192.168.100.120</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>admin-Ppond</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.0.0.0</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.0.0.1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.0.0.2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>H3C</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.0.0.3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>192.168.0.54</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>micky-niggaa</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>gAAAAABpAstM--OOOSvble6tFHb82_3ok7KzM19A_Qdg6smi8Q5nAPUB4T53VL20DydUfnvdqJb_QbcPHs7--tT56g46HJ6j8g==</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,28 +528,6 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>192.168.0.54</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>micky-niggaa</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>gAAAAABpAstM--OOOSvble6tFHb82_3ok7KzM19A_Qdg6smi8Q5nAPUB4T53VL20DydUfnvdqJb_QbcPHs7--tT56g46HJ6j8g==</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dataset.xlsx
+++ b/dataset.xlsx
@@ -1,43 +1,454 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
+  <si>
+    <t>Brand</t>
+  </si>
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Cisco</t>
+  </si>
+  <si>
+    <t>192.168.100.120</t>
+  </si>
+  <si>
+    <t>admin-Ppond</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>192.168.100.121</t>
+  </si>
+  <si>
+    <t>HPE</t>
+  </si>
+  <si>
+    <t>192.168.100.122</t>
+  </si>
+  <si>
+    <t>admin-mixky</t>
+  </si>
+  <si>
+    <t>192.168.100.123</t>
+  </si>
+  <si>
+    <t>H3C</t>
+  </si>
+  <si>
+    <t>192.168.100.124</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;฿&quot;* #,##0.00_-;\-&quot;฿&quot;* #,##0.00_-;_-&quot;฿&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;฿&quot;* #,##0_-;\-&quot;฿&quot;* #,##0_-;_-&quot;฿&quot;* &quot;-&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="22">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -46,93 +457,329 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="เครื่องหมายจุลภาค" xfId="1" builtinId="3"/>
+    <cellStyle name="เครื่องหมายสกุลเงิน" xfId="2" builtinId="4"/>
+    <cellStyle name="เปอร์เซ็นต์" xfId="3" builtinId="5"/>
+    <cellStyle name="เครื่องหมายจุลภาค [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="เครื่องหมายสกุลเงิน [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="การเชื่อมโยงหลายมิติ" xfId="6" builtinId="8"/>
+    <cellStyle name="การเชื่อมโยงหลายมิติที่ตาม" xfId="7" builtinId="9"/>
+    <cellStyle name="หมายเหตุ" xfId="8" builtinId="10"/>
+    <cellStyle name="ข้อความเตือน" xfId="9" builtinId="11"/>
+    <cellStyle name="ชื่อเรื่อง" xfId="10" builtinId="15"/>
+    <cellStyle name="ข้อความอธิบาย" xfId="11" builtinId="53"/>
+    <cellStyle name="หัวเรื่อง 1" xfId="12" builtinId="16"/>
+    <cellStyle name="หัวเรื่อง 2" xfId="13" builtinId="17"/>
+    <cellStyle name="หัวเรื่อง 3" xfId="14" builtinId="18"/>
+    <cellStyle name="หัวเรื่อง 4" xfId="15" builtinId="19"/>
+    <cellStyle name="ป้อนค่า" xfId="16" builtinId="20"/>
+    <cellStyle name="แสดงผล" xfId="17" builtinId="21"/>
+    <cellStyle name="การคำนวณ" xfId="18" builtinId="22"/>
+    <cellStyle name="เซลล์ตรวจสอบ" xfId="19" builtinId="23"/>
+    <cellStyle name="เซลล์ที่มีลิงก์" xfId="20" builtinId="24"/>
+    <cellStyle name="ผลรวม" xfId="21" builtinId="25"/>
+    <cellStyle name="ดี" xfId="22" builtinId="26"/>
+    <cellStyle name="แย่" xfId="23" builtinId="27"/>
+    <cellStyle name="ปานกลาง" xfId="24" builtinId="28"/>
+    <cellStyle name="ส่วนที่ถูกเน้น1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - ส่วนที่ถูกเน้น1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - ส่วนที่ถูกเน้น1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - ส่วนที่ถูกเน้น1" xfId="28" builtinId="32"/>
+    <cellStyle name="ส่วนที่ถูกเน้น2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - ส่วนที่ถูกเน้น2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - ส่วนที่ถูกเน้น2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - ส่วนที่ถูกเน้น2" xfId="32" builtinId="36"/>
+    <cellStyle name="ส่วนที่ถูกเน้น3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - ส่วนที่ถูกเน้น3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - ส่วนที่ถูกเน้น3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - ส่วนที่ถูกเน้น3" xfId="36" builtinId="40"/>
+    <cellStyle name="ส่วนที่ถูกเน้น4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - ส่วนที่ถูกเน้น4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - ส่วนที่ถูกเน้น4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - ส่วนที่ถูกเน้น4" xfId="40" builtinId="44"/>
+    <cellStyle name="ส่วนที่ถูกเน้น5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - ส่วนที่ถูกเน้น5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - ส่วนที่ถูกเน้น5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - ส่วนที่ถูกเน้น5" xfId="44" builtinId="48"/>
+    <cellStyle name="ส่วนที่ถูกเน้น6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - ส่วนที่ถูกเน้น6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - ส่วนที่ถูกเน้น6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - ส่วนที่ถูกเน้น6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -415,120 +1062,104 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="5" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="16.8" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="13.2" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>IP</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Username</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Password</t>
-        </is>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>192.168.100.120</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>admin-Ppond</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0.0.0.0</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>HPE</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0.0.0.1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>HPE</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.0.0.2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5"/>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>H3C</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.0.0.3</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>